--- a/upload/report/test_hiraoka18.xlsx
+++ b/upload/report/test_hiraoka18.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>Purchase order items PDF to Excel</t>
   </si>
@@ -23,7 +23,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02 19:27:54</t>
+    <t>2024-04-03 11:34:49</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>#Order</t>
   </si>
   <si>
     <t>Num</t>
@@ -44,7 +53,16 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>CALLE 5, MZ. D-1, LOTE 5 - COOP., LAS VER VILLA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>132867</t>
   </si>
   <si>
     <t>1</t>
@@ -65,7 +83,7 @@
     <t>81,002.00</t>
   </si>
   <si>
-    <t>TELEVISOR LED NANOCELL LG - 50NANO77SRA 15 15 20</t>
+    <t>TELEVISOR LED NANOCELL LG - 50NANO77SRA</t>
   </si>
   <si>
     <t>2</t>
@@ -83,7 +101,7 @@
     <t>102,594.00</t>
   </si>
   <si>
-    <t>TELEVISOR LED UHD LG - 50UR7300PSA 25 20 20 10</t>
+    <t>TELEVISOR LED UHD LG - 50UR7300PSA</t>
   </si>
   <si>
     <t>3</t>
@@ -101,7 +119,7 @@
     <t>80,320.41</t>
   </si>
   <si>
-    <t>TELEVISOR OLED LG - OLED55C3PSA 5 4 3 5</t>
+    <t>TELEVISOR OLED LG - OLED55C3PSA</t>
   </si>
   <si>
     <t>4</t>
@@ -119,7 +137,7 @@
     <t>115,672.05</t>
   </si>
   <si>
-    <t>TELEVISOR QNED NANOCELL LG - 55QNED80SRA 10 10 10 15</t>
+    <t>TELEVISOR QNED NANOCELL LG - 55QNED80SRA</t>
   </si>
   <si>
     <t>5</t>
@@ -137,7 +155,7 @@
     <t>104,226.90</t>
   </si>
   <si>
-    <t>TELEVISOR QNED NANOCELL LG - 65QNED90SQA 12 3</t>
+    <t>TELEVISOR QNED NANOCELL LG - 65QNED90SQA</t>
   </si>
   <si>
     <t>6</t>
@@ -495,15 +513,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -511,7 +529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -533,143 +551,206 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
       <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
